--- a/rapporten/prijsrapport-2026-04-19.xlsx
+++ b/rapporten/prijsrapport-2026-04-19.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="59">
   <si>
     <t>Product</t>
   </si>
@@ -188,15 +188,6 @@
   </si>
   <si>
     <t>1831682</t>
-  </si>
-  <si>
-    <t>8719214751654</t>
-  </si>
-  <si>
-    <t>8721055493488</t>
-  </si>
-  <si>
-    <t>1762224</t>
   </si>
 </sst>
 </file>
@@ -588,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1823,58 +1814,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" t="s">
-        <v>59</v>
-      </c>
-      <c r="C48" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="D48" s="1">
-        <v>12.25</v>
-      </c>
-      <c r="E48" s="1">
-        <v>0.25</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-      <c r="G48" s="1">
-        <v>12.25</v>
-      </c>
-      <c r="H48" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>60</v>
-      </c>
-      <c r="B49" t="s">
-        <v>60</v>
-      </c>
-      <c r="C49" s="1">
-        <v>11.59</v>
-      </c>
-      <c r="D49" s="1">
-        <v>11.58</v>
-      </c>
-      <c r="E49" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="F49" t="s">
-        <v>61</v>
-      </c>
-      <c r="G49" s="1">
-        <v>11.58</v>
-      </c>
-      <c r="H49" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
